--- a/untranslated/downloads/data-excel/2.1.2.c.xlsx
+++ b/untranslated/downloads/data-excel/2.1.2.c.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E0D857-0E03-45D3-9408-A8CB88AE8A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2.1.2.1d " sheetId="4" r:id="rId1"/>
@@ -122,12 +123,6 @@
     <t>Fish and products of their processing</t>
   </si>
   <si>
-    <t>2.1.2.1d Ratio of agricultural products import to total production in the country</t>
-  </si>
-  <si>
-    <t>2.1.2.1d Отношение объема импорта продукции сельского хозяйства к объему производства в республике</t>
-  </si>
-  <si>
     <t>Дан жана кайра иштетилген продуктылар</t>
   </si>
   <si>
@@ -161,9 +156,6 @@
     <t>Балык жана аларды кайра иштетүү продуктылары</t>
   </si>
   <si>
-    <t>2.1.2.1d Айыл чарба продукциясынын импортунун көлөмүнүн өлкөдөгү өндүрүштүн көлөмүнө катышы</t>
-  </si>
-  <si>
     <t>(в процентах)</t>
   </si>
   <si>
@@ -172,11 +164,20 @@
   <si>
     <t>(in percent)</t>
   </si>
+  <si>
+    <t>2.1.2.c Ratio of agricultural products import to total production in the country</t>
+  </si>
+  <si>
+    <t>2.1.2.c Отношение объема импорта продукции сельского хозяйства к объему производства в республике</t>
+  </si>
+  <si>
+    <t>2.1.2.c Айыл чарба продукциясынын импортунун көлөмүнүн өлкөдөгү өндүрүштүн көлөмүнө катышы</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
@@ -311,44 +312,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -357,36 +354,35 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Normal 17" xfId="3"/>
+    <cellStyle name="Normal 17" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 2 2" xfId="2"/>
-    <cellStyle name="Обычный 7" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 7" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -402,7 +398,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Data"/>
@@ -7867,9 +7863,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7907,9 +7903,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -7944,7 +7940,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -7979,7 +7975,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8152,511 +8148,429 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="40.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="3" width="40.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>25</v>
+    <row r="1" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>39</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
-    <row r="3" spans="1:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+    <row r="3" spans="1:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="18">
         <v>2018</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="19">
         <v>2019</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="19">
         <v>2020</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="19">
         <v>2021</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="19">
         <v>2022</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="19">
         <v>2023</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="8">
+        <v>16.602255280851288</v>
+      </c>
+      <c r="E5" s="9">
+        <v>18.656793703396851</v>
+      </c>
+      <c r="F5" s="9">
+        <v>21.55202470488619</v>
+      </c>
+      <c r="G5" s="10">
+        <v>35.5</v>
+      </c>
+      <c r="H5" s="4">
+        <v>32.9</v>
+      </c>
+      <c r="I5" s="4">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="8">
+        <v>47.264166260756625</v>
+      </c>
+      <c r="E6" s="9">
+        <v>52.844311377245504</v>
+      </c>
+      <c r="F6" s="9">
+        <v>57.606103958035284</v>
+      </c>
+      <c r="G6" s="10">
+        <v>104.9</v>
+      </c>
+      <c r="H6" s="4">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="I6" s="4">
+        <v>108.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="9">
-        <v>16.602255280851288</v>
-      </c>
-      <c r="E5" s="10">
-        <v>18.656793703396851</v>
-      </c>
-      <c r="F5" s="10">
-        <v>21.55202470488619</v>
-      </c>
-      <c r="G5" s="11">
-        <v>35.5</v>
-      </c>
-      <c r="H5" s="5">
-        <v>32.9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="B7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="8">
+        <v>37.90771678599841</v>
+      </c>
+      <c r="E7" s="9">
+        <v>68.831168831168839</v>
+      </c>
+      <c r="F7" s="9">
+        <v>46.079136690647481</v>
+      </c>
+      <c r="G7" s="10">
+        <v>66.5</v>
+      </c>
+      <c r="H7" s="4">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="I7" s="4">
+        <v>81.2</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+    <row r="8" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="9">
-        <v>47.264166260756625</v>
-      </c>
-      <c r="E6" s="10">
-        <v>52.844311377245504</v>
-      </c>
-      <c r="F6" s="10">
-        <v>57.606103958035284</v>
-      </c>
-      <c r="G6" s="11">
-        <v>104.9</v>
-      </c>
-      <c r="H6" s="5">
-        <v>75.400000000000006</v>
-      </c>
-      <c r="I6" s="5">
-        <v>108.5</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="B8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.72583990045624225</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0.98267578978017189</v>
+      </c>
+      <c r="F8" s="9">
+        <v>1.311030741410488</v>
+      </c>
+      <c r="G8" s="10">
+        <v>2.7228298813125438</v>
+      </c>
+      <c r="H8" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="I8" s="4">
+        <v>2.5</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="24" t="s">
+    <row r="9" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="8">
+        <v>3.9360119047619047</v>
+      </c>
+      <c r="E9" s="9">
+        <v>6.0098593591416556</v>
+      </c>
+      <c r="F9" s="9">
+        <v>7.0366913190206075</v>
+      </c>
+      <c r="G9" s="10">
+        <v>8.692405346874768</v>
+      </c>
+      <c r="H9" s="4">
+        <v>10.6</v>
+      </c>
+      <c r="I9" s="4">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="8">
+        <v>15.047446904654313</v>
+      </c>
+      <c r="E10" s="9">
+        <v>18.656056587091072</v>
+      </c>
+      <c r="F10" s="9">
+        <v>16.623263888888886</v>
+      </c>
+      <c r="G10" s="10">
+        <v>19.2</v>
+      </c>
+      <c r="H10" s="4">
+        <v>23.5</v>
+      </c>
+      <c r="I10" s="4">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.0127697049757818</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.7999754269566286</v>
+      </c>
+      <c r="F11" s="9">
+        <v>3.2254196642685846</v>
+      </c>
+      <c r="G11" s="13">
+        <v>1.8</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="I11" s="4">
         <v>2</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="9">
-        <v>37.90771678599841</v>
-      </c>
-      <c r="E7" s="10">
-        <v>68.831168831168839</v>
-      </c>
-      <c r="F7" s="10">
-        <v>46.079136690647481</v>
-      </c>
-      <c r="G7" s="11">
-        <v>66.5</v>
-      </c>
-      <c r="H7" s="5">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="I7" s="5">
-        <v>81.2</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0.72583990045624225</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0.98267578978017189</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1.311030741410488</v>
-      </c>
-      <c r="G8" s="11">
-        <v>2.7228298813125438</v>
-      </c>
-      <c r="H8" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="I8" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+    <row r="12" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.623375035443543</v>
+      </c>
+      <c r="E12" s="12">
+        <v>6.7791389127971886</v>
+      </c>
+      <c r="F12" s="12">
+        <v>11.599852469612779</v>
+      </c>
+      <c r="G12" s="10">
+        <v>16.3</v>
+      </c>
+      <c r="H12" s="4">
+        <v>29.2</v>
+      </c>
+      <c r="I12" s="4">
+        <v>32.299999999999997</v>
+      </c>
     </row>
-    <row r="9" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="9">
-        <v>3.9360119047619047</v>
-      </c>
-      <c r="E9" s="10">
-        <v>6.0098593591416556</v>
-      </c>
-      <c r="F9" s="10">
-        <v>7.0366913190206075</v>
-      </c>
-      <c r="G9" s="11">
-        <v>8.692405346874768</v>
-      </c>
-      <c r="H9" s="5">
-        <v>10.6</v>
-      </c>
-      <c r="I9" s="5">
-        <v>11.1</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+    <row r="13" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="8">
+        <v>66.938775510204081</v>
+      </c>
+      <c r="E13" s="12">
+        <v>56.224899598393577</v>
+      </c>
+      <c r="F13" s="13">
+        <v>49.707602339181292</v>
+      </c>
+      <c r="G13" s="10">
+        <v>142.6</v>
+      </c>
+      <c r="H13" s="4">
+        <v>110.7</v>
+      </c>
+      <c r="I13" s="4">
+        <v>89</v>
+      </c>
     </row>
-    <row r="10" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="9">
-        <v>15.047446904654313</v>
-      </c>
-      <c r="E10" s="10">
-        <v>18.656056587091072</v>
-      </c>
-      <c r="F10" s="10">
-        <v>16.623263888888886</v>
-      </c>
-      <c r="G10" s="11">
-        <v>19.2</v>
-      </c>
-      <c r="H10" s="5">
-        <v>23.5</v>
-      </c>
-      <c r="I10" s="5">
-        <v>23.4</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+    <row r="14" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="8">
+        <v>396.58119658119659</v>
+      </c>
+      <c r="E14" s="12">
+        <v>528.72340425531922</v>
+      </c>
+      <c r="F14" s="13">
+        <v>897.4</v>
+      </c>
+      <c r="G14" s="10">
+        <v>1018.6</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1120</v>
+      </c>
+      <c r="I14" s="4">
+        <v>989.2</v>
+      </c>
     </row>
-    <row r="11" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="9">
-        <v>1.0127697049757818</v>
-      </c>
-      <c r="E11" s="10">
-        <v>1.7999754269566286</v>
-      </c>
-      <c r="F11" s="10">
-        <v>3.2254196642685846</v>
-      </c>
-      <c r="G11" s="15">
-        <v>1.8</v>
-      </c>
-      <c r="H11" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="I11" s="5">
-        <v>2</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+    <row r="15" spans="1:9" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="15">
+        <v>171.18742724097788</v>
+      </c>
+      <c r="E15" s="16">
+        <v>109.83027341170255</v>
+      </c>
+      <c r="F15" s="16">
+        <v>84.63334435862015</v>
+      </c>
+      <c r="G15" s="17">
+        <v>30.1</v>
+      </c>
+      <c r="H15" s="17">
+        <v>14.5</v>
+      </c>
+      <c r="I15" s="17">
+        <v>11</v>
+      </c>
     </row>
-    <row r="12" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0.623375035443543</v>
-      </c>
-      <c r="E12" s="13">
-        <v>6.7791389127971886</v>
-      </c>
-      <c r="F12" s="13">
-        <v>11.599852469612779</v>
-      </c>
-      <c r="G12" s="11">
-        <v>16.3</v>
-      </c>
-      <c r="H12" s="5">
-        <v>29.2</v>
-      </c>
-      <c r="I12" s="5">
-        <v>32.299999999999997</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
     </row>
-    <row r="13" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="9">
-        <v>66.938775510204081</v>
-      </c>
-      <c r="E13" s="13">
-        <v>56.224899598393577</v>
-      </c>
-      <c r="F13" s="15">
-        <v>49.707602339181292</v>
-      </c>
-      <c r="G13" s="11">
-        <v>142.6</v>
-      </c>
-      <c r="H13" s="5">
-        <v>110.7</v>
-      </c>
-      <c r="I13" s="5">
-        <v>89</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
-    <row r="14" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="9">
-        <v>396.58119658119659</v>
-      </c>
-      <c r="E14" s="13">
-        <v>528.72340425531922</v>
-      </c>
-      <c r="F14" s="15">
-        <v>897.4</v>
-      </c>
-      <c r="G14" s="11">
-        <v>1018.6</v>
-      </c>
-      <c r="H14" s="5">
-        <v>1120</v>
-      </c>
-      <c r="I14" s="5">
-        <v>989.2</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="17">
-        <v>171.18742724097788</v>
-      </c>
-      <c r="E15" s="18">
-        <v>109.83027341170255</v>
-      </c>
-      <c r="F15" s="18">
-        <v>84.63334435862015</v>
-      </c>
-      <c r="G15" s="19">
-        <v>30.1</v>
-      </c>
-      <c r="H15" s="19">
-        <v>14.5</v>
-      </c>
-      <c r="I15" s="19">
-        <v>11</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/untranslated/downloads/data-excel/2.1.2.c.xlsx
+++ b/untranslated/downloads/data-excel/2.1.2.c.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E0D857-0E03-45D3-9408-A8CB88AE8A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2592C0B5-7C85-41CE-8F55-E2070D2B1173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,7 +182,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,6 +278,29 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -287,7 +310,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -304,6 +327,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -312,7 +344,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -376,6 +408,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal 17" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -8149,7 +8198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="40.7109375" style="3" customWidth="1"/>
@@ -8159,7 +8208,7 @@
     <col min="8" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
@@ -8174,7 +8223,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
         <v>37</v>
       </c>
@@ -8189,7 +8238,7 @@
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -8199,8 +8248,9 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
+      <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>11</v>
       </c>
@@ -8228,8 +8278,11 @@
       <c r="I4" s="19">
         <v>2023</v>
       </c>
+      <c r="J4" s="19">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>25</v>
       </c>
@@ -8240,25 +8293,28 @@
         <v>14</v>
       </c>
       <c r="D5" s="8">
-        <v>16.602255280851288</v>
+        <v>9.4</v>
       </c>
       <c r="E5" s="9">
-        <v>18.656793703396851</v>
+        <v>12.9</v>
       </c>
       <c r="F5" s="9">
-        <v>21.55202470488619</v>
+        <v>12.2</v>
       </c>
       <c r="G5" s="10">
-        <v>35.5</v>
-      </c>
-      <c r="H5" s="4">
-        <v>32.9</v>
-      </c>
-      <c r="I5" s="4">
-        <v>34.799999999999997</v>
+        <v>24.2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>19.3</v>
+      </c>
+      <c r="I5" s="3">
+        <v>29.7</v>
+      </c>
+      <c r="J5" s="26">
+        <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>26</v>
       </c>
@@ -8269,25 +8325,28 @@
         <v>15</v>
       </c>
       <c r="D6" s="8">
-        <v>47.264166260756625</v>
+        <v>26.1</v>
       </c>
       <c r="E6" s="9">
-        <v>52.844311377245504</v>
+        <v>34.9</v>
       </c>
       <c r="F6" s="9">
-        <v>57.606103958035284</v>
+        <v>28</v>
       </c>
       <c r="G6" s="10">
-        <v>104.9</v>
-      </c>
-      <c r="H6" s="4">
-        <v>75.400000000000006</v>
-      </c>
-      <c r="I6" s="4">
-        <v>108.5</v>
+        <v>61.6</v>
+      </c>
+      <c r="H6" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="I6" s="3">
+        <v>92</v>
+      </c>
+      <c r="J6" s="3">
+        <v>53.8</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
         <v>27</v>
       </c>
@@ -8298,25 +8357,28 @@
         <v>16</v>
       </c>
       <c r="D7" s="8">
-        <v>37.90771678599841</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="E7" s="9">
-        <v>68.831168831168839</v>
+        <v>63.8</v>
       </c>
       <c r="F7" s="9">
-        <v>46.079136690647481</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="G7" s="10">
-        <v>66.5</v>
-      </c>
-      <c r="H7" s="4">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="I7" s="4">
-        <v>81.2</v>
+        <v>43.2</v>
+      </c>
+      <c r="H7" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="I7" s="29">
+        <v>47.1</v>
+      </c>
+      <c r="J7" s="3">
+        <v>46.8</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>28</v>
       </c>
@@ -8327,25 +8389,28 @@
         <v>17</v>
       </c>
       <c r="D8" s="8">
-        <v>0.72583990045624225</v>
+        <v>0.2</v>
       </c>
       <c r="E8" s="9">
-        <v>0.98267578978017189</v>
+        <v>0.1</v>
       </c>
       <c r="F8" s="9">
-        <v>1.311030741410488</v>
+        <v>0.3</v>
       </c>
       <c r="G8" s="10">
-        <v>2.7228298813125438</v>
-      </c>
-      <c r="H8" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="I8" s="4">
-        <v>2.5</v>
+        <v>0.7</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
         <v>29</v>
       </c>
@@ -8356,25 +8421,28 @@
         <v>18</v>
       </c>
       <c r="D9" s="8">
-        <v>3.9360119047619047</v>
+        <v>3.2</v>
       </c>
       <c r="E9" s="9">
-        <v>6.0098593591416556</v>
+        <v>4.7</v>
       </c>
       <c r="F9" s="9">
-        <v>7.0366913190206075</v>
+        <v>6.5</v>
       </c>
       <c r="G9" s="10">
-        <v>8.692405346874768</v>
-      </c>
-      <c r="H9" s="4">
-        <v>10.6</v>
-      </c>
-      <c r="I9" s="4">
-        <v>11.1</v>
+        <v>8</v>
+      </c>
+      <c r="H9" s="3">
+        <v>9.9</v>
+      </c>
+      <c r="I9" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="J9" s="3">
+        <v>6.8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>30</v>
       </c>
@@ -8385,25 +8453,28 @@
         <v>19</v>
       </c>
       <c r="D10" s="8">
-        <v>15.047446904654313</v>
+        <v>15.1</v>
       </c>
       <c r="E10" s="9">
-        <v>18.656056587091072</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="F10" s="9">
-        <v>16.623263888888886</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="G10" s="10">
         <v>19.2</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="3">
         <v>23.5</v>
       </c>
-      <c r="I10" s="4">
-        <v>23.4</v>
+      <c r="I10" s="3">
+        <v>23.6</v>
+      </c>
+      <c r="J10" s="3">
+        <v>34.1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>31</v>
       </c>
@@ -8414,25 +8485,28 @@
         <v>20</v>
       </c>
       <c r="D11" s="8">
-        <v>1.0127697049757818</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E11" s="9">
-        <v>1.7999754269566286</v>
+        <v>1.5</v>
       </c>
       <c r="F11" s="9">
-        <v>3.2254196642685846</v>
+        <v>2.4</v>
       </c>
       <c r="G11" s="13">
         <v>1.8</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="3">
         <v>1.8</v>
       </c>
-      <c r="I11" s="4">
-        <v>2</v>
+      <c r="I11" s="26">
+        <v>3.2</v>
+      </c>
+      <c r="J11" s="3">
+        <v>3.1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="22" t="s">
         <v>32</v>
       </c>
@@ -8454,14 +8528,17 @@
       <c r="G12" s="10">
         <v>16.3</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="3">
         <v>29.2</v>
       </c>
-      <c r="I12" s="4">
-        <v>32.299999999999997</v>
+      <c r="I12" s="26">
+        <v>34</v>
+      </c>
+      <c r="J12" s="26">
+        <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>33</v>
       </c>
@@ -8471,26 +8548,29 @@
       <c r="C13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="8">
-        <v>66.938775510204081</v>
-      </c>
-      <c r="E13" s="12">
-        <v>56.224899598393577</v>
-      </c>
-      <c r="F13" s="13">
-        <v>49.707602339181292</v>
-      </c>
-      <c r="G13" s="10">
-        <v>142.6</v>
-      </c>
-      <c r="H13" s="4">
-        <v>110.7</v>
-      </c>
-      <c r="I13" s="4">
-        <v>89</v>
+      <c r="D13" s="30">
+        <v>26.367346938775508</v>
+      </c>
+      <c r="E13" s="31">
+        <v>26.606425702811247</v>
+      </c>
+      <c r="F13" s="32">
+        <v>32.163742690058484</v>
+      </c>
+      <c r="G13" s="33">
+        <v>61.265432098765437</v>
+      </c>
+      <c r="H13" s="27">
+        <v>71.694599627560521</v>
+      </c>
+      <c r="I13" s="27">
+        <v>52.450331125827823</v>
+      </c>
+      <c r="J13" s="27">
+        <v>54.147465437788021</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>34</v>
       </c>
@@ -8512,14 +8592,17 @@
       <c r="G14" s="10">
         <v>1018.6</v>
       </c>
-      <c r="H14" s="4">
-        <v>1120</v>
-      </c>
-      <c r="I14" s="4">
+      <c r="H14" s="3">
+        <v>936.7</v>
+      </c>
+      <c r="I14" s="3">
         <v>989.2</v>
       </c>
+      <c r="J14" s="3">
+        <v>801.1</v>
+      </c>
     </row>
-    <row r="15" spans="1:9" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>35</v>
       </c>
@@ -8530,25 +8613,28 @@
         <v>24</v>
       </c>
       <c r="D15" s="15">
-        <v>171.18742724097788</v>
+        <v>157.69230769230768</v>
       </c>
       <c r="E15" s="16">
-        <v>109.83027341170255</v>
+        <v>106.66666666666667</v>
       </c>
       <c r="F15" s="16">
-        <v>84.63334435862015</v>
+        <v>82.352941176470594</v>
       </c>
       <c r="G15" s="17">
-        <v>30.1</v>
+        <v>24.271844660194173</v>
       </c>
       <c r="H15" s="17">
-        <v>14.5</v>
+        <v>13.043478260869568</v>
       </c>
       <c r="I15" s="17">
-        <v>11</v>
+        <v>10.089020771513352</v>
+      </c>
+      <c r="J15" s="28">
+        <v>33.862433862433868</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
